--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260914.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.65%</t>
+          <t>9.73%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.41%</t>
+          <t>9.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>6.60%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.71%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.01%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>64,742,000</t>
+          <t>32,456,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,88 +887,88 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>32,456,000</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,729,000</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,767</t>
+          <t>26,729,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>202610TX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>233,108,056</t>
+          <t>1,767</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -997,66 +997,66 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>84,590,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>84,590,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,705,000</t>
+          <t>254,199,845</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>254,199,845</t>
+          <t>35,705,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,388,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>53,388,000</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,525,159,087</t>
+          <t>10,388,430,716</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,443,020,390</t>
+          <t>6,293,106,029</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-341,614,308</t>
+          <t>-239,050,656</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
